--- a/results/ch4_solver_SA01.xlsx
+++ b/results/ch4_solver_SA01.xlsx
@@ -18,6 +18,8 @@
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_tol" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">5</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">'モデル'!$M$29:$M$45</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">2</definedName>

--- a/results/ch4_solver_SA01.xlsx
+++ b/results/ch4_solver_SA01.xlsx
@@ -519,7 +519,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ビンの寸法を選ぶ（SA-01、寸法候補8種類）― Excelソルバー版</t>
+          <t>部品箱の寸法を選ぶ（SA-01、寸法候補8種類）― Excelソルバー版</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ビン1個の面積（ブロック）</t>
+          <t>部品箱1個の面積（ブロック）</t>
         </is>
       </c>
       <c r="E5" s="6" t="n">
@@ -578,7 +578,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>① 必要なビンの数 n（前計算。空欄＝入らない）</t>
+          <t>① 必要な部品箱の数 n（前計算。空欄＝入らない）</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>② x：部品をその寸法のビンに入れるか（0/1、変数セル）</t>
+          <t>② x：部品をその寸法の部品箱に入れるか（0/1、変数セル）</t>
         </is>
       </c>
     </row>
